--- a/data/trans_orig/P36BPD03_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023</t>
+          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50145</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45971</t>
+          <t>45818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77340</t>
+          <t>77949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136613</t>
+          <t>137062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183525</t>
+          <t>183132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117065</t>
+          <t>118254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151565</t>
+          <t>152003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>266727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>323651</t>
+          <t>321532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>279147</t>
+          <t>278092</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337780</t>
+          <t>336420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>340738</t>
+          <t>341987</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>385346</t>
+          <t>383660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>629915</t>
+          <t>629485</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>701631</t>
+          <t>702466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113116</t>
+          <t>110202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164960</t>
+          <t>166034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134375</t>
+          <t>134012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169321</t>
+          <t>170225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255832</t>
+          <t>259129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323040</t>
+          <t>322600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70665</t>
+          <t>69297</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>19900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>38161</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50489</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98270</t>
+          <t>99713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115646</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>289768</t>
+          <t>294035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145939</t>
+          <t>146146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186820</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261833</t>
+          <t>245457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>451592</t>
+          <t>455188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598791</t>
+          <t>593930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>936784</t>
+          <t>960491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529305</t>
+          <t>531053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581165</t>
+          <t>581388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1157763</t>
+          <t>1160226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1578861</t>
+          <t>1592708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109533</t>
+          <t>103155</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>254500</t>
+          <t>258033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187287</t>
+          <t>185670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230897</t>
+          <t>229735</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>259798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>468505</t>
+          <t>462314</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37439</t>
+          <t>37191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72391</t>
+          <t>73504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70977</t>
+          <t>70486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64178</t>
+          <t>66111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130490</t>
+          <t>132108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>150806</t>
+          <t>151032</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>205935</t>
+          <t>205505</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>77628</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>207205</t>
+          <t>208769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>219942</t>
+          <t>225556</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>389449</t>
+          <t>395745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284314</t>
+          <t>285531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>346534</t>
+          <t>346674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>211268</t>
+          <t>193181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>499989</t>
+          <t>502931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>441344</t>
+          <t>445221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>812509</t>
+          <t>810849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138158</t>
+          <t>135831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188358</t>
+          <t>189065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184199</t>
+          <t>179890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>637972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339838</t>
+          <t>340224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>903442</t>
+          <t>874915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>46760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80951</t>
+          <t>81060</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34493</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>61930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>87811</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133292</t>
+          <t>132521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201284</t>
+          <t>201391</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262324</t>
+          <t>259451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173131</t>
+          <t>171126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244294</t>
+          <t>241247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>390781</t>
+          <t>388549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485803</t>
+          <t>486507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>394643</t>
+          <t>399754</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>460572</t>
+          <t>463225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>532707</t>
+          <t>534623</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>679525</t>
+          <t>673780</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>952010</t>
+          <t>953232</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1121562</t>
+          <t>1126466</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180889</t>
+          <t>178332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>236212</t>
+          <t>232740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>206891</t>
+          <t>208932</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284179</t>
+          <t>285380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>403856</t>
+          <t>405052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>500834</t>
+          <t>500647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>146993</t>
+          <t>147908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>232120</t>
+          <t>231074</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122314</t>
+          <t>119156</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178828</t>
+          <t>176357</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>292912</t>
+          <t>289812</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>391298</t>
+          <t>396371</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>615160</t>
+          <t>611618</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>873605</t>
+          <t>873185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>552938</t>
+          <t>539289</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>729524</t>
+          <t>727584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1270836</t>
+          <t>1259283</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1572321</t>
+          <t>1560238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1634802</t>
+          <t>1630212</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2159107</t>
+          <t>2174827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1568687</t>
+          <t>1516610</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2025855</t>
+          <t>2013123</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3370696</t>
+          <t>3338519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3982010</t>
+          <t>4033644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>546491</t>
+          <t>515693</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>771246</t>
+          <t>769711</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>786749</t>
+          <t>792028</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1443537</t>
+          <t>1492821</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1445624</t>
+          <t>1451596</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2160847</t>
+          <t>2320061</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD03_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59799</t>
+          <t>61757</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45818</t>
+          <t>47763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77949</t>
+          <t>79452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>158547</t>
+          <t>166443</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137062</t>
+          <t>144611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183132</t>
+          <t>193986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134167</t>
+          <t>140805</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118254</t>
+          <t>122548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152003</t>
+          <t>159728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>292714</t>
+          <t>307248</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266727</t>
+          <t>278212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>321532</t>
+          <t>339114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>306987</t>
+          <t>332774</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>278092</t>
+          <t>307321</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>336420</t>
+          <t>359918</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>362183</t>
+          <t>394946</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>341987</t>
+          <t>371532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>383660</t>
+          <t>417325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>669171</t>
+          <t>727720</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>629485</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>702466</t>
+          <t>764982</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>135888</t>
+          <t>156818</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110202</t>
+          <t>131440</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>166034</t>
+          <t>185211</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>150770</t>
+          <t>167305</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134012</t>
+          <t>149940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170225</t>
+          <t>187712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>286658</t>
+          <t>324124</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259129</t>
+          <t>292073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322600</t>
+          <t>359789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>633670</t>
+          <t>688859</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>633670</t>
+          <t>688859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>633670</t>
+          <t>688859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674672</t>
+          <t>731990</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674672</t>
+          <t>731990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674672</t>
+          <t>731990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1308342</t>
+          <t>1420850</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1308342</t>
+          <t>1420850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1308342</t>
+          <t>1420850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>33674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69297</t>
+          <t>64068</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>74420</t>
+          <t>76523</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>59991</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99713</t>
+          <t>97432</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>221226</t>
+          <t>226490</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112186</t>
+          <t>198233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>294035</t>
+          <t>259764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>165229</t>
+          <t>178696</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146146</t>
+          <t>157751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187033</t>
+          <t>202017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>386455</t>
+          <t>405186</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245457</t>
+          <t>369634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>455188</t>
+          <t>442714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>731331</t>
+          <t>550436</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>593930</t>
+          <t>513896</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>960491</t>
+          <t>585743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>555582</t>
+          <t>624327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531053</t>
+          <t>596233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581388</t>
+          <t>653690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1286913</t>
+          <t>1174763</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1160226</t>
+          <t>1121559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1592708</t>
+          <t>1221833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>192954</t>
+          <t>224068</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103155</t>
+          <t>195763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>258033</t>
+          <t>258620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>207475</t>
+          <t>236147</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185670</t>
+          <t>212140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229735</t>
+          <t>259298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>400428</t>
+          <t>460215</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>259798</t>
+          <t>421697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>462314</t>
+          <t>501158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>956160</t>
+          <t>1068775</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>956160</t>
+          <t>1068775</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>956160</t>
+          <t>1068775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2148216</t>
+          <t>2116687</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2148216</t>
+          <t>2116687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2148216</t>
+          <t>2116687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>55747</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37191</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73504</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47358</t>
+          <t>49578</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70486</t>
+          <t>68826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>99470</t>
+          <t>105325</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66111</t>
+          <t>84480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132108</t>
+          <t>130639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>178533</t>
+          <t>191121</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151032</t>
+          <t>166322</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>205505</t>
+          <t>218833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>152907</t>
+          <t>171667</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77628</t>
+          <t>151403</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>208769</t>
+          <t>193881</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>331441</t>
+          <t>362788</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>225556</t>
+          <t>325619</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>395745</t>
+          <t>397713</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>314229</t>
+          <t>359856</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>285531</t>
+          <t>328278</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>346674</t>
+          <t>396094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>378545</t>
+          <t>404326</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193181</t>
+          <t>379320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>502931</t>
+          <t>433996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>692774</t>
+          <t>764182</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>445221</t>
+          <t>718382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>810849</t>
+          <t>803230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>159806</t>
+          <t>196348</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135831</t>
+          <t>169034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189065</t>
+          <t>224922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>354556</t>
+          <t>186689</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179890</t>
+          <t>164925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>637972</t>
+          <t>207469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>514362</t>
+          <t>383037</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>340224</t>
+          <t>347930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>874915</t>
+          <t>422425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>61564</t>
+          <t>63329</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81060</t>
+          <t>83178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>50661</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35037</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61930</t>
+          <t>65313</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>113989</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87811</t>
+          <t>94329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132521</t>
+          <t>135578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229821</t>
+          <t>232055</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201391</t>
+          <t>203216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259451</t>
+          <t>264555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>212150</t>
+          <t>223975</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171126</t>
+          <t>201062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>241247</t>
+          <t>250139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>441970</t>
+          <t>456030</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388549</t>
+          <t>420735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>486507</t>
+          <t>499333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -2658,67 +2658,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>429329</t>
+          <t>470893</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>399754</t>
+          <t>438273</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>463225</t>
+          <t>505282</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>51,13%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>559221</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>527915</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>588102</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>50,03%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>580180</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>534623</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>673780</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>53,05%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1009509</t>
+          <t>1030113</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>953232</t>
+          <t>984114</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1126466</t>
+          <t>1073415</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>205245</t>
+          <t>221947</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178332</t>
+          <t>193841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232740</t>
+          <t>250641</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>254472</t>
+          <t>283856</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208932</t>
+          <t>258952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>285380</t>
+          <t>310689</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>459717</t>
+          <t>505803</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405052</t>
+          <t>467494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>500647</t>
+          <t>549799</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>925959</t>
+          <t>988224</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>925959</t>
+          <t>988224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>925959</t>
+          <t>988224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1093679</t>
+          <t>1117712</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1093679</t>
+          <t>1117712</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1093679</t>
+          <t>1117712</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2019638</t>
+          <t>2105935</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2019638</t>
+          <t>2105935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2019638</t>
+          <t>2105935</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>192468</t>
+          <t>198818</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>231074</t>
+          <t>229718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>149662</t>
+          <t>158776</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>119156</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>183486</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>342130</t>
+          <t>357595</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>289812</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>396371</t>
+          <t>401872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>788127</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>611618</t>
+          <t>762333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>873185</t>
+          <t>876476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>664452</t>
+          <t>715142</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>539289</t>
+          <t>673310</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>727584</t>
+          <t>761989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1452580</t>
+          <t>1531252</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1259283</t>
+          <t>1463105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1560238</t>
+          <t>1604072</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1781878</t>
+          <t>1713959</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1630212</t>
+          <t>1649591</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2174827</t>
+          <t>1774853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1876489</t>
+          <t>1982819</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1516610</t>
+          <t>1928696</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2013123</t>
+          <t>2036507</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3658368</t>
+          <t>3696778</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3338519</t>
+          <t>3609249</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4033644</t>
+          <t>3787107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>693893</t>
+          <t>799182</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>515693</t>
+          <t>743701</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>769711</t>
+          <t>859366</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>967272</t>
+          <t>873997</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>792028</t>
+          <t>826194</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1492821</t>
+          <t>915618</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1661166</t>
+          <t>1673179</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1451596</t>
+          <t>1600795</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2320061</t>
+          <t>1746180</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
